--- a/diseases/d146/2026-2029.xlsx
+++ b/diseases/d146/2026-2029.xlsx
@@ -5686,6 +5686,151 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>disseminated-cryptococcosis</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>播散性隐球菌病</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5719,7 +5864,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5947,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -5812,7 +5957,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -5864,7 +6009,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d146/2026-2029.xlsx
+++ b/diseases/d146/2026-2029.xlsx
@@ -5831,6 +5831,151 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>disseminated-cryptococcosis</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>播散性隐球菌病</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.002450425222697299</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5864,7 +6009,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5947,7 +6092,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -5957,7 +6102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -6009,7 +6154,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d146/2026-2029.xlsx
+++ b/diseases/d146/2026-2029.xlsx
@@ -5976,6 +5976,151 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>disseminated-cryptococcosis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>播散性隐球菌病</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6009,7 +6154,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6237,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6102,7 +6247,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -6154,7 +6299,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d146/2026-2029.xlsx
+++ b/diseases/d146/2026-2029.xlsx
@@ -6121,6 +6121,151 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>disseminated-cryptococcosis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>播散性隐球菌病</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6154,7 +6299,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6382,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -6247,7 +6392,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -6299,7 +6444,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d146/2026-2029.xlsx
+++ b/diseases/d146/2026-2029.xlsx
@@ -6266,6 +6266,151 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>disseminated-cryptococcosis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>播散性隐球菌病</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6299,7 +6444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6527,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -6392,7 +6537,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -6444,7 +6589,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d146/2026-2029.xlsx
+++ b/diseases/d146/2026-2029.xlsx
@@ -6411,6 +6411,151 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>disseminated-cryptococcosis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Disseminated cryptococcosis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>播散性隐球菌病</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6444,7 +6589,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6672,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -6537,7 +6682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -6589,7 +6734,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
